--- a/docs/EXECUTION_SURFACES_L2.xlsx
+++ b/docs/EXECUTION_SURFACES_L2.xlsx
@@ -788,13 +788,14 @@
       </c>
       <c r="D15" s="4" t="inlineStr"/>
     </row>
-    <row r="17" ht="75" customHeight="1">
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Legend: Parity column colours — green Parallel, yellow Conditional, orange Divergent. Layers M0–M14 are the pass-2 layers (prefix M to
 keep them apart from pass 1's L0–L17); Pipeline steps are the pass-2 sequence in order (constants → adapter columns → sync → apply → lab
-snapshot → bins → parity → gold MERGE → equality → property → StackSync → schedule); Remediation rows T01– record what the CRM evidence
-of 2026-10-16 corrected. Source: branch claude/cloud-run-bigquery-pipeline-e94ziy at 2026-10-16; CRM hub 9201667 via the HubSpot connector.
+snapshot → bins → parity → gold MERGE → equality → property → StackSync → schedule; 13–15 are pass 2b, 2026-10-22: the company object by
+foreign-key resolution — one SQL body, the notebook dry run over @deals_payload, the shipped views and snapshot, the scheduled refresh);
+Remediation rows T01– record what the CRM evidence of 2026-10-16 corrected (T13: what the operator's notebook cell corrected). Source: branch claude/cloud-run-bigquery-pipeline-e94ziy at 2026-10-16; CRM hub 9201667 via the HubSpot connector.
 </t>
         </is>
       </c>
@@ -819,9 +820,9 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
@@ -841,12 +842,12 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>N · Vertex AI Workbench notebook notebooks/l2_deal_tiers.ipynb (lab — HubSpot API snapshot, numpy.digitize, calibration, deal_tiers_lab)</t>
+          <t>N · Vertex AI Workbench / Colab Enterprise notebooks (l2_deal_tiers.ipynb — the lab: HubSpot API snapshot, numpy.digitize, calibration, deal_tiers_lab; company_tiers.ipynb — pass 2b: dry run over @deals_payload, ship, equality, refresh gates)</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Q · BigQuery-native (sql/deal_tiers_v1.sql views + sql/deal_tiers_apply.sql scheduled MERGE over the daily HubSpot → BigQuery transfer)</t>
+          <t>Q · BigQuery-native (sql/deal_tiers_v1.sql views + sql/deal_tiers_apply.sql scheduled MERGE over the daily HubSpot → BigQuery transfer; pass 2b: company_tiers_v1 views + sql/company_tiers_apply.sql scheduled refresh)</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1575,7 +1576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1607,12 +1608,12 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>N · Vertex AI Workbench notebook notebooks/l2_deal_tiers.ipynb (lab — HubSpot API snapshot, numpy.digitize, calibration, deal_tiers_lab) — cell</t>
+          <t>N · Vertex AI Workbench / Colab Enterprise notebooks (l2_deal_tiers.ipynb — the lab: HubSpot API snapshot, numpy.digitize, calibration, deal_tiers_lab; company_tiers.ipynb — pass 2b: dry run over @deals_payload, ship, equality, refresh gates) — cell</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Q · BigQuery-native (sql/deal_tiers_v1.sql views + sql/deal_tiers_apply.sql scheduled MERGE over the daily HubSpot → BigQuery transfer) — command</t>
+          <t>Q · BigQuery-native (sql/deal_tiers_v1.sql views + sql/deal_tiers_apply.sql scheduled MERGE over the daily HubSpot → BigQuery transfer; pass 2b: company_tiers_v1 views + sql/company_tiers_apply.sql scheduled refresh) — command</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
@@ -2151,6 +2152,137 @@
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>company body</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>notebooks/company_tiers.ipynb §0 renders sql/company_tiers_body.sql the way sql/apply.sh does (the include spliced, the placeholders substituted) — the notebook holds no copy of the rule</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>sql/company_tiers_body.sql — one CTE chain over a deal_source the including statement defines (14 columns, in order): labels → the ARR staging (stg_deals) → the icalps_dealstatus rule → three resolvers → resolved → rollup (sales_region × entity_key × tier, the deals nested)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>tests/test_company_tiers.py green: both assemblies render; the view's input columns == the documented deal_source columns == the notebook's payload fields, in order; resolver precedence 1_primary_assoc → 2_clinic_fc_map → 3_direct_company_name → 4_unresolved_fc → 5_no_fc_or_company; no DDL/DML on a sync table</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>The operator's cell had added derived columns to the synced Deals table (T13); the rule now lives in the dataset, once, and every surface includes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>company dry run · ship · equality</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>LIVE DDL</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>notebook §1 snapshot via main.HubSpot tiered as deal_tiers_v1 would → §2 the body over UNNEST(@deals_payload) (ARRAY&lt;STRUCT&gt;, statement_type = SELECT asserted; deal-level and company-level CSVs; "0 BigQuery tables written") → §3 ship = sql/company_tiers_v1.sql rendered as apply.sh renders it → §4 equality: the dry run's rollup vs company_tiers_v1 per sales_region × entity_key × tier</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>sql/apply.sh applies sql/company_tiers_v1.sql when SYNC_COMPANIES_TABLE is set (companies_synced_v1, company_deal_input_v1, company_deals_v1, company_tiers_v1, company_tiers, company_tiers_history, company_tiers_refreshes, company_tiers_summary_v1); skipped with a notice otherwise</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>INFORMATION_SCHEMA lists the eight objects; §4 prints identical n_deals per group when the snapshot and the sync are of the same state (otherwise differences explained by deals created, edited, deleted or re-associated in between)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Same rule, two sources (the API snapshot, the sync); the Companies asset must have transferred once (SYNC_COMPANIES_TABLE) and the ARR staging must be readable (ARR_DATASET).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>company refresh</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>LIVE SCHEDULE</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>notebook §5: DRYRUN=1 sql/company_tiers_schedule.sh → gate flag → DISABLE_SCHEDULE=1 register (paused) + one manual refresh (the rendered apply with run_time) → §6 probe (company_tiers_refreshes, the summary view, the snapshot CSV) → §7 gate flag → the script without DISABLE_SCHEDULE (auto-scheduling on)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>sql/company_tiers_apply.sql as the scheduled query company-tiers-refresh (SCHEDULE_UTC_COMPANY_TIERS, default every day 03:37 UTC, refused on the hour; SA new-deals-sql@ with dataEditor on the dataset, dataViewer on the sync and ARR datasets): 36 h freshness guard, TEMP batch from the view, row-count guard, one transaction (snapshot replaced, history slice, refreshes row), EXCEPTION → ROLLBACK + FAILED row + RAISE</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Divergent</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>bq ls --transfer_config shows company-tiers-refresh; company_tiers_refreshes holds one OK row per run (n_rows, n_companies, n_unresolved, n_deals, duration_ms); company_tiers_history gains one slice per refresh</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>The pass-3 pattern (register paused → one manual run → probe → enable), with the probe on a standalone notebook kernel instead of Cloud Shell. Nothing is written into a sync table.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2163,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2656,6 +2788,43 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>The operator's notebook cell ALTERed the synced Deals table (unified_probability, tier, … added) and MERGEd a CSV into it, then built vw_company_tiers_v1 / mv_company_tiers_v1 on those columns; the next transfer run overwrites the sync table, and the rule existed only in the cell</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>N Q</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Derived columns written into a transfer-owned table; a third copy of the tiering (lab, lane Q, the cell) with no test keeping them equal.</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Pass 2b: the rule once in sql/company_tiers_body.sql, included by the views (Q) and by the notebook's dry run over @deals_payload (N); the derived columns live in company_tiers (dataset objects, refreshed by sql/company_tiers_apply.sql); tests/test_company_tiers.py asserts no DDL/DML on a sync table and the same input columns on every surface.</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>this commit — tests green; the notebook has not yet run against wisekeybq</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2667,7 +2836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2690,12 +2859,12 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>N · Vertex AI Workbench notebook notebooks/l2_deal_tiers.ipynb (lab — HubSpot API snapshot, numpy.digitize, calibration, deal_tiers_lab) — cell</t>
+          <t>N · Vertex AI Workbench / Colab Enterprise notebooks (l2_deal_tiers.ipynb — the lab: HubSpot API snapshot, numpy.digitize, calibration, deal_tiers_lab; company_tiers.ipynb — pass 2b: dry run over @deals_payload, ship, equality, refresh gates) — cell</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Q · BigQuery-native (sql/deal_tiers_v1.sql views + sql/deal_tiers_apply.sql scheduled MERGE over the daily HubSpot → BigQuery transfer) / W · Webhook CDC (HubSpot deal.propertyChange on dealstage / icalps_oppocertainty → Cloud Run function event path → MERGE one deal) — command</t>
+          <t>Q · BigQuery-native (sql/deal_tiers_v1.sql views + sql/deal_tiers_apply.sql scheduled MERGE over the daily HubSpot → BigQuery transfer; pass 2b: company_tiers_v1 views + sql/company_tiers_apply.sql scheduled refresh) / W · Webhook CDC (HubSpot deal.propertyChange on dealstage / icalps_oppocertainty → Cloud Run function event path → MERGE one deal) — command</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -2809,6 +2978,33 @@
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>identical per label</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>after the company dry run and the ship (pass 2b)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>n_deals per sales_region × entity_key × tier — the dry run over @deals_payload (N, the API snapshot) vs company_tiers_v1 (Q, the sync)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>notebook §4 (outer join on the three keys; rows where the counts differ listed)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SELECT sales_region, entity_key, tier, n_deals, resolver FROM company_tiers_v1 ORDER BY 1, 2, 3</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>identical when the snapshot and the sync are of the same state; otherwise differences explained by deals created, edited, deleted or re-associated between the transfer and the snapshot; the resolver per row equal on both sides</t>
         </is>
       </c>
     </row>
